--- a/assets/constructions/examples/ctd_bs_adapter_coolantb.xlsx
+++ b/assets/constructions/examples/ctd_bs_adapter_coolantb.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHS MB50-R80</t>
+          <t>CHS MB63-R80</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,45 +582,45 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>28.5</v>
+        <v>37</v>
       </c>
       <c r="I2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="K2" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="L2" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DAN_MB50</t>
+          <t>DAN_MB80</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>DAN_MB50</t>
+          <t>DAN_MB63</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>DAN_MB50</t>
+          <t>DAN_MB63</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -616,10 +636,10 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="U2" t="n">
-        <v>3.3</v>
+        <v>5.16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -629,6 +649,12 @@
           <t>2020 / www.iscar.com</t>
         </is>
       </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,11 +740,17 @@
           <t>2020 / www.iscar.com</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHS MB63-R80</t>
+          <t>CHS MB50-R80</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -732,45 +764,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
         <v>80</v>
       </c>
-      <c r="F4" t="n">
-        <v>63</v>
-      </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>37</v>
+        <v>28.5</v>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="J4" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DAN_MB80</t>
+          <t>DAN_MB50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>DAN_MB63</t>
+          <t>DAN_MB50</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>DAN_MB63</t>
+          <t>DAN_MB50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -786,10 +818,10 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="U4" t="n">
-        <v>5.16</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,6 +831,12 @@
           <t>2020 / www.iscar.com</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
